--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-20T17:48:12+00:00</t>
+    <t>2023-01-25T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -436,11 +436,11 @@
     <t>PertinenciaAtencionBox</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolean}
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolPertinenciaAtencionBox}
 </t>
   </si>
   <si>
-    <t>ExtBoolean</t>
+    <t>ExtBool Pertinencia Atencion Box</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -450,11 +450,11 @@
     <t>MotivoNoPertinencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtString}
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtStringMotivoNoPertinencia}
 </t>
   </si>
   <si>
-    <t>ExtString</t>
+    <t>ExtString MotivoNoPertinencia</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -711,6 +711,9 @@
   </si>
   <si>
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
+  </si>
+  <si>
+    <t>in-progress</t>
   </si>
   <si>
     <t>Current state of the encounter.</t>
@@ -4304,7 +4307,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4349,7 +4352,7 @@
         <v>76</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>76</v>
@@ -4367,10 +4370,10 @@
         <v>172</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>76</v>
@@ -4403,21 +4406,21 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4440,16 +4443,16 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -4499,7 +4502,7 @@
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
@@ -4528,7 +4531,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4637,7 +4640,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4748,11 +4751,11 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4774,10 +4777,10 @@
         <v>127</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>145</v>
@@ -4832,7 +4835,7 @@
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4861,7 +4864,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4920,10 +4923,10 @@
         <v>172</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>76</v>
@@ -4941,7 +4944,7 @@
         <v>76</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>82</v>
@@ -4970,7 +4973,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4996,10 +4999,10 @@
         <v>206</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -5050,7 +5053,7 @@
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>82</v>
@@ -5079,7 +5082,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5102,13 +5105,13 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -5138,10 +5141,10 @@
         <v>183</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>76</v>
@@ -5159,7 +5162,7 @@
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>82</v>
@@ -5177,18 +5180,18 @@
         <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5211,13 +5214,13 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5268,7 +5271,7 @@
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
@@ -5297,7 +5300,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5406,7 +5409,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5517,11 +5520,11 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5543,10 +5546,10 @@
         <v>127</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>145</v>
@@ -5601,7 +5604,7 @@
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5653,13 +5656,13 @@
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -5689,10 +5692,10 @@
         <v>183</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>76</v>
@@ -5710,7 +5713,7 @@
         <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>82</v>
@@ -5739,7 +5742,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5765,10 +5768,10 @@
         <v>206</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5819,7 +5822,7 @@
         <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>82</v>
@@ -5848,7 +5851,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5874,13 +5877,13 @@
         <v>178</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
@@ -5906,13 +5909,13 @@
         <v>76</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>76</v>
@@ -5930,7 +5933,7 @@
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
@@ -5945,21 +5948,21 @@
         <v>94</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5985,10 +5988,10 @@
         <v>178</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -6015,13 +6018,13 @@
         <v>76</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>76</v>
@@ -6039,7 +6042,7 @@
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -6054,7 +6057,7 @@
         <v>94</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>161</v>
@@ -6063,12 +6066,12 @@
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6094,10 +6097,10 @@
         <v>178</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6124,13 +6127,13 @@
         <v>76</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>76</v>
@@ -6148,7 +6151,7 @@
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
@@ -6166,22 +6169,22 @@
         <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6200,16 +6203,16 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6259,7 +6262,7 @@
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>74</v>
@@ -6274,21 +6277,21 @@
         <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6311,13 +6314,13 @@
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6368,7 +6371,7 @@
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
@@ -6383,25 +6386,25 @@
         <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>161</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6420,13 +6423,13 @@
         <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6477,7 +6480,7 @@
         <v>76</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>74</v>
@@ -6492,10 +6495,10 @@
         <v>94</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6506,7 +6509,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6529,13 +6532,13 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -6586,7 +6589,7 @@
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
@@ -6601,21 +6604,21 @@
         <v>94</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6724,7 +6727,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6835,11 +6838,11 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6861,10 +6864,10 @@
         <v>127</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M45" t="s" s="2">
         <v>145</v>
@@ -6919,7 +6922,7 @@
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
@@ -6948,7 +6951,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6974,13 +6977,13 @@
         <v>178</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7009,10 +7012,10 @@
         <v>183</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>76</v>
@@ -7030,7 +7033,7 @@
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>74</v>
@@ -7045,21 +7048,21 @@
         <v>94</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7085,10 +7088,10 @@
         <v>206</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7139,7 +7142,7 @@
         <v>76</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
@@ -7157,18 +7160,18 @@
         <v>76</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7191,13 +7194,13 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7248,7 +7251,7 @@
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>74</v>
@@ -7263,21 +7266,21 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7300,13 +7303,13 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -7357,7 +7360,7 @@
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>74</v>
@@ -7372,21 +7375,21 @@
         <v>94</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7412,13 +7415,13 @@
         <v>206</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -7468,7 +7471,7 @@
         <v>76</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>74</v>
@@ -7483,21 +7486,21 @@
         <v>94</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7520,16 +7523,16 @@
         <v>76</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -7579,7 +7582,7 @@
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>74</v>
@@ -7594,25 +7597,25 @@
         <v>94</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7634,13 +7637,13 @@
         <v>178</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
@@ -7669,10 +7672,10 @@
         <v>106</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>76</v>
@@ -7690,7 +7693,7 @@
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>74</v>
@@ -7705,25 +7708,25 @@
         <v>94</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7742,16 +7745,16 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
@@ -7801,7 +7804,7 @@
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>74</v>
@@ -7816,21 +7819,21 @@
         <v>94</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7853,13 +7856,13 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
@@ -7910,7 +7913,7 @@
         <v>76</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>74</v>
@@ -7928,7 +7931,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7939,7 +7942,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8048,7 +8051,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8159,11 +8162,11 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8185,10 +8188,10 @@
         <v>127</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>145</v>
@@ -8243,7 +8246,7 @@
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>74</v>
@@ -8272,11 +8275,11 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8295,16 +8298,16 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
@@ -8354,7 +8357,7 @@
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>82</v>
@@ -8369,21 +8372,21 @@
         <v>94</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8409,10 +8412,10 @@
         <v>178</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8442,10 +8445,10 @@
         <v>106</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>76</v>
@@ -8463,7 +8466,7 @@
         <v>76</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>74</v>
@@ -8492,7 +8495,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8515,13 +8518,13 @@
         <v>76</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8572,7 +8575,7 @@
         <v>76</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>74</v>
@@ -8590,7 +8593,7 @@
         <v>76</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8601,7 +8604,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8624,16 +8627,16 @@
         <v>76</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
@@ -8683,7 +8686,7 @@
         <v>76</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>74</v>
@@ -8701,7 +8704,7 @@
         <v>76</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8712,7 +8715,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -8735,16 +8738,16 @@
         <v>76</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
@@ -8794,7 +8797,7 @@
         <v>76</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>74</v>
@@ -8812,7 +8815,7 @@
         <v>76</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8823,7 +8826,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -8932,7 +8935,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9043,11 +9046,11 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9069,10 +9072,10 @@
         <v>127</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>145</v>
@@ -9127,7 +9130,7 @@
         <v>76</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>74</v>
@@ -9156,7 +9159,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9182,10 +9185,10 @@
         <v>149</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9236,7 +9239,7 @@
         <v>76</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>74</v>
@@ -9260,12 +9263,12 @@
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9288,13 +9291,13 @@
         <v>76</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9345,7 +9348,7 @@
         <v>76</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>74</v>
@@ -9363,7 +9366,7 @@
         <v>76</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
@@ -9374,7 +9377,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9400,10 +9403,10 @@
         <v>178</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -9433,10 +9436,10 @@
         <v>106</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>76</v>
@@ -9454,7 +9457,7 @@
         <v>76</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>74</v>
@@ -9472,18 +9475,18 @@
         <v>76</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9509,10 +9512,10 @@
         <v>178</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9539,13 +9542,13 @@
         <v>76</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>76</v>
@@ -9563,7 +9566,7 @@
         <v>76</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>74</v>
@@ -9587,12 +9590,12 @@
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9618,16 +9621,16 @@
         <v>178</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>76</v>
@@ -9652,13 +9655,13 @@
         <v>76</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>76</v>
@@ -9676,7 +9679,7 @@
         <v>76</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>74</v>
@@ -9694,18 +9697,18 @@
         <v>76</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -9731,10 +9734,10 @@
         <v>178</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -9764,10 +9767,10 @@
         <v>106</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>76</v>
@@ -9785,7 +9788,7 @@
         <v>76</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>74</v>
@@ -9803,18 +9806,18 @@
         <v>76</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -9840,10 +9843,10 @@
         <v>178</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -9873,10 +9876,10 @@
         <v>106</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>76</v>
@@ -9894,7 +9897,7 @@
         <v>76</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>74</v>
@@ -9912,18 +9915,18 @@
         <v>76</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -9946,13 +9949,13 @@
         <v>76</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -10003,7 +10006,7 @@
         <v>76</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>74</v>
@@ -10021,18 +10024,18 @@
         <v>76</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10058,10 +10061,10 @@
         <v>178</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10088,13 +10091,13 @@
         <v>76</v>
       </c>
       <c r="W74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>76</v>
@@ -10112,7 +10115,7 @@
         <v>76</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>74</v>
@@ -10130,18 +10133,18 @@
         <v>76</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10164,16 +10167,16 @@
         <v>76</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
@@ -10223,7 +10226,7 @@
         <v>76</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>74</v>
@@ -10241,7 +10244,7 @@
         <v>76</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>76</v>
@@ -10252,7 +10255,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10361,7 +10364,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10472,11 +10475,11 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10498,10 +10501,10 @@
         <v>127</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>145</v>
@@ -10556,7 +10559,7 @@
         <v>76</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>74</v>
@@ -10585,7 +10588,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -10608,13 +10611,13 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -10665,7 +10668,7 @@
         <v>76</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>82</v>
@@ -10680,21 +10683,21 @@
         <v>94</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -10720,13 +10723,13 @@
         <v>102</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -10755,10 +10758,10 @@
         <v>172</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>76</v>
@@ -10776,7 +10779,7 @@
         <v>76</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>74</v>
@@ -10794,7 +10797,7 @@
         <v>76</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>76</v>
@@ -10805,7 +10808,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -10831,13 +10834,13 @@
         <v>178</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
@@ -10863,13 +10866,13 @@
         <v>76</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>76</v>
@@ -10887,7 +10890,7 @@
         <v>76</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>74</v>
@@ -10916,7 +10919,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -10942,10 +10945,10 @@
         <v>206</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -10996,7 +10999,7 @@
         <v>76</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>74</v>
@@ -11014,7 +11017,7 @@
         <v>76</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>76</v>
@@ -11025,7 +11028,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11051,10 +11054,10 @@
         <v>213</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -11105,7 +11108,7 @@
         <v>76</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>74</v>
@@ -11120,21 +11123,21 @@
         <v>94</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11157,16 +11160,16 @@
         <v>76</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
@@ -11216,7 +11219,7 @@
         <v>76</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>74</v>
@@ -11231,10 +11234,10 @@
         <v>94</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>76</v>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
   </si>
   <si>
-    <t>in-progress</t>
+    <t>finished</t>
   </si>
   <si>
     <t>Current state of the encounter.</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/refs/heads/main/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
